--- a/modele_salaire.xlsx
+++ b/modele_salaire.xlsx
@@ -94,7 +94,7 @@
     <t>MARCELLI DAVID</t>
   </si>
   <si>
-    <t>LAUBEUF THIMOTE</t>
+    <t>BERNARDO VASCO</t>
   </si>
   <si>
     <t>ETAM</t>
